--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:52</t>
+    <t xml:space="preserve">2026-08-28 11:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:41</t>
+    <t xml:space="preserve">2026-09-01 13:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:27</t>
+    <t xml:space="preserve">2026-09-03 12:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
+++ b/output/graficos_regionales_migracion_flujos/plot_migracion_flujos_od_2021_los_rios.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-03 12:20</t>
+    <t xml:space="preserve">2026-09-07 09:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
